--- a/Sajjad data/by_country_and_state/USA/MT.xlsx
+++ b/Sajjad data/by_country_and_state/USA/MT.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="261">
   <si>
     <t>Business Name</t>
   </si>
@@ -374,6 +374,426 @@
   </si>
   <si>
     <t>2026-10-25T04:20:30.082Z</t>
+  </si>
+  <si>
+    <t>Brewer Kevin M DDS</t>
+  </si>
+  <si>
+    <t>(406) 656-6100</t>
+  </si>
+  <si>
+    <t>710 Main St #1, Billings, MT 59105</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Brewer+Kevin+M+DDS/data=!4m7!3m6!1s0x53487a8e87bc5af9:0xc40b18d1d06a7a66!8m2!3d45.8114992!4d-108.4726088!16s%2Fg%2F12638qxmc!19sChIJ-Vq8h456SFMRZnpq0NEYC8Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:15.057Z</t>
+  </si>
+  <si>
+    <t>Greg Zlock Dentistry D.M.D</t>
+  </si>
+  <si>
+    <t>(406) 543-6320</t>
+  </si>
+  <si>
+    <t>1211 S Reserve St #201, Missoula, MT 59801</t>
+  </si>
+  <si>
+    <t>Missoula</t>
+  </si>
+  <si>
+    <t>SundayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Greg+Zlock+Dentistry+D.M.D/data=!4m7!3m6!1s0x535dcdfc62c77e5f:0xbcfad4891e662bf4!8m2!3d46.8606071!4d-114.0405807!16s%2Fg%2F1tfd21n9!19sChIJX37HYvzNXVMR9CtmHonU-rw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:34.329Z</t>
+  </si>
+  <si>
+    <t>Dr. Ryan K. Huckeby, DMD</t>
+  </si>
+  <si>
+    <t>(406) 728-9442</t>
+  </si>
+  <si>
+    <t>1227 S Higgins Ave, Missoula, MT 59801</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Ryan+K.+Huckeby,+DMD/data=!4m7!3m6!1s0x535dcdcedb4d22eb:0x8cf5f4a7b85ed51e!8m2!3d46.8587633!4d-113.9978231!16s%2Fg%2F1tczdkxg!19sChIJ6yJN287NXVMRHtVeuKf09Yw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:36.641Z</t>
+  </si>
+  <si>
+    <t>Nanette B. Ault PC, DDS</t>
+  </si>
+  <si>
+    <t>(406) 549-4867</t>
+  </si>
+  <si>
+    <t>Dental implants periodontist</t>
+  </si>
+  <si>
+    <t>619 SW Higgins Ave # G, Missoula, MT 59803</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>SundayClosed; Monday8 AM–5 PM; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; Friday8 AM–5 PM; SaturdayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nanette+B.+Ault+PC,+DDS/data=!4m7!3m6!1s0x535dcd997d543b83:0x325de7cac90709b0!8m2!3d46.83733!4d-114.007311!16s%2Fg%2F1tdc09g3!19sChIJgztUfZnNXVMRsAkHycrnXTI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:39.043Z</t>
+  </si>
+  <si>
+    <t>Dr. Matthew L. Heaphy, DDS</t>
+  </si>
+  <si>
+    <t>(406) 543-8347</t>
+  </si>
+  <si>
+    <t>712 Kensington Ave, Missoula, MT 59801</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Matthew+L.+Heaphy,+DDS/data=!4m7!3m6!1s0x535dcdc11a0504cf:0x2d52881ad95b329f!8m2!3d46.8534943!4d-114.0085643!16s%2Fg%2F1tdbknn1!19sChIJzwQFGsHNXVMRnzJb2RqIUi0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:41.336Z</t>
+  </si>
+  <si>
+    <t>Dr. Mark Messer DMD</t>
+  </si>
+  <si>
+    <t>(406) 549-6081</t>
+  </si>
+  <si>
+    <t>1547 S Higgins Ave, Missoula, MT 59801</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Mark+Messer+DMD/data=!4m7!3m6!1s0x535dcdbd04067fcf:0x757721d6f768242a!8m2!3d46.8562293!4d-113.997831!16s%2Fg%2F11bbt8c1hh!19sChIJz38GBL3NXVMRKiRo99Yhd3U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:43.502Z</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Dental Lab</t>
+  </si>
+  <si>
+    <t>(406) 728-2751</t>
+  </si>
+  <si>
+    <t>Dental laboratory</t>
+  </si>
+  <si>
+    <t>750 Kensington Ave, Missoula, MT 59801</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rocky+Mountain+Dental+Lab/data=!4m7!3m6!1s0x535dcdc10fdd54c7:0x8cb0eac2338f19db!8m2!3d46.8536011!4d-114.0093876!16s%2Fg%2F1ttdy37z!19sChIJx1TdD8HNXVMR2xmPM8LqsIw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:45.393Z</t>
+  </si>
+  <si>
+    <t>Funseth Dental</t>
+  </si>
+  <si>
+    <t>(406) 454-3711</t>
+  </si>
+  <si>
+    <t>114 13th St S, Great Falls, MT 59401</t>
+  </si>
+  <si>
+    <t>Great Falls</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Funseth+Dental/data=!4m7!3m6!1s0x5342370059ba1981:0x5d39d6dc698be624!8m2!3d47.5034246!4d-111.2854755!16s%2Fg%2F11xgfz40fq!19sChIJgRm6WQA3QlMRJOaLadzWOV0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:18.075Z</t>
+  </si>
+  <si>
+    <t>Great Falls Dental Associates</t>
+  </si>
+  <si>
+    <t>(406) 452-8740</t>
+  </si>
+  <si>
+    <t>Dental clinic</t>
+  </si>
+  <si>
+    <t>1601 2nd Ave N #100, Great Falls, MT 59401</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Great+Falls+Dental+Associates/data=!4m7!3m6!1s0x5342370060f5983d:0x3f2cca392c5f82d0!8m2!3d47.5077331!4d-111.279067!16s%2Fg%2F11y3_h6pr9!19sChIJPZj1YAA3QlMR0IJfLDnKLD8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:20.225Z</t>
+  </si>
+  <si>
+    <t>Dr. Aimee R. Ameline, DDS.</t>
+  </si>
+  <si>
+    <t>(406) 761-4288</t>
+  </si>
+  <si>
+    <t>613 Park Dr S, Great Falls, MT 59405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Aimee+R.+Ameline,+DDS./data=!4m7!3m6!1s0x534237ae9da86209:0x6af338304f2bac75!8m2!3d47.4983449!4d-111.3050483!16s%2Fg%2F1tftd_20!19sChIJCWKona43QlMRdawrTzA482o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:22.483Z</t>
+  </si>
+  <si>
+    <t>Bryan K. Pike, D.D.S.</t>
+  </si>
+  <si>
+    <t>(406) 727-5343</t>
+  </si>
+  <si>
+    <t>2615 16th Ave S, Great Falls, MT 59405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bryan+K.+Pike,+D.D.S./data=!4m7!3m6!1s0x534237ae9e2dd721:0x3f629137be0461c3!8m2!3d47.4884356!4d-111.2613866!16s%2Fg%2F1tjthyms!19sChIJIdctnq43QlMRw2EEvjeRYj8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:25.445Z</t>
+  </si>
+  <si>
+    <t>Electric City Dental Laboratory</t>
+  </si>
+  <si>
+    <t>(406) 452-7122</t>
+  </si>
+  <si>
+    <t>1704 9th Ave S, Great Falls, MT 59405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Electric+City+Dental+Laboratory/data=!4m7!3m6!1s0x5342370909b0a9bf:0x8530f92b4b87fcac!8m2!3d47.4950037!4d-111.2778114!16s%2Fg%2F11cnwc_772!19sChIJv6mwCQk3QlMRrPyHSyv5MIU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:28.200Z</t>
+  </si>
+  <si>
+    <t>Neil Robin R DDS</t>
+  </si>
+  <si>
+    <t>(406) 454-1512</t>
+  </si>
+  <si>
+    <t>910 1st Ave N Ste 212, Great Falls, MT 59401</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Neil+Robin+R+DDS/data=!4m7!3m6!1s0x534237525b251f99:0xe052a32041327662!8m2!3d47.5066361!4d-111.298732!16s%2Fg%2F11t4gmw8qr!19sChIJmR8lW1I3QlMRYnYyQSCjUuA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:30.461Z</t>
+  </si>
+  <si>
+    <t>David Wayne Johnson DDS</t>
+  </si>
+  <si>
+    <t>(406) 761-1091</t>
+  </si>
+  <si>
+    <t>2800 11th Ave S Ste 24, Great Falls, MT 59405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/David+Wayne+Johnson+DDS/data=!4m7!3m6!1s0x534237a88b446549:0x64018ed2965c08af!8m2!3d47.4921955!4d-111.2584384!16s%2Fg%2F1thw1tpp!19sChIJSWVEi6g3QlMRrwhcltKOAWQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:34.498Z</t>
+  </si>
+  <si>
+    <t>Elkin Carrie Ann DDS</t>
+  </si>
+  <si>
+    <t>(406) 452-3003</t>
+  </si>
+  <si>
+    <t>2500 Bobcat Way, Great Falls, MT 59405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Elkin+Carrie+Ann+DDS/data=!4m7!3m6!1s0x534237beab58e5c7:0x7905bd2956a3f597!8m2!3d47.4857997!4d-111.2642774!16s%2Fg%2F1td37xh3!19sChIJx-VYq743QlMRl_WjVim9BXk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:48.440Z</t>
+  </si>
+  <si>
+    <t>Bailey a Eugene DDS</t>
+  </si>
+  <si>
+    <t>(406) 761-3131</t>
+  </si>
+  <si>
+    <t>2523 6th Ave S #2, Great Falls, MT 59405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bailey+a+Eugene+DDS/data=!4m7!3m6!1s0x534237a0d7b3a52f:0xfc52d27acb533e3d!8m2!3d47.4988074!4d-111.2631892!16s%2Fg%2F1th491j9!19sChIJL6Wz16A3QlMRPT5Ty3rSUvw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:50.930Z</t>
+  </si>
+  <si>
+    <t>Coleman Robert M DDS</t>
+  </si>
+  <si>
+    <t>(406) 452-2964</t>
+  </si>
+  <si>
+    <t>2523 6th Ave S, Great Falls, MT 59405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Coleman+Robert+M+DDS/data=!4m7!3m6!1s0x534237a0d7b3a52f:0x7610cb3b7c3843c6!8m2!3d47.4988074!4d-111.2631892!16s%2Fg%2F1tdgzz4v!19sChIJL6Wz16A3QlMRxkM4fDvLEHY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:52.753Z</t>
+  </si>
+  <si>
+    <t>Kenneth C Small PC</t>
+  </si>
+  <si>
+    <t>(406) 452-2138</t>
+  </si>
+  <si>
+    <t>2527 6th Ave S, Great Falls, MT 59405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kenneth+C+Small+PC/data=!4m7!3m6!1s0x534237a0d13ffc15:0x50e187e4b75ca2b2!8m2!3d47.498883!4d-111.2628395!16s%2Fg%2F1thgb3f7!19sChIJFfw_0aA3QlMRsqJct-SH4VA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:55.308Z</t>
+  </si>
+  <si>
+    <t>Lisa Linstroth, DMD</t>
+  </si>
+  <si>
+    <t>(406) 452-5361</t>
+  </si>
+  <si>
+    <t>3920 3rd Ave S, Great Falls, MT 59405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lisa+Linstroth,+DMD/data=!4m7!3m6!1s0x53423711349e3e57:0xa4b63417718cd952!8m2!3d47.5014017!4d-111.2386853!16s%2Fg%2F11c2nt3jgp!19sChIJVz6eNBE3QlMRUtmMcRc0tqQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:04:19.915Z</t>
+  </si>
+  <si>
+    <t>Dental Park: Wolgamot Thomas C DDS</t>
+  </si>
+  <si>
+    <t>(406) 727-2444</t>
+  </si>
+  <si>
+    <t>2501 6th Ave S, Great Falls, MT 59405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Park:+Wolgamot+Thomas+C+DDS/data=!4m7!3m6!1s0x534237a128e80e19:0x6958bb3cf0d5a559!8m2!3d47.4986721!4d-111.2638345!16s%2Fg%2F1wbf_1tt!19sChIJGQ7oKKE3QlMRWaXV8Dy7WGk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:04:22.415Z</t>
+  </si>
+  <si>
+    <t>Dr. carreen M. elof, DDS</t>
+  </si>
+  <si>
+    <t>+33 9 72 10 89 90</t>
+  </si>
+  <si>
+    <t>299-201 10th St S, Great Falls, MT 59405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+carreen+M.+elof,+DDS/data=!4m7!3m6!1s0x5342371fcc0df8e9:0xd94ab7eb2362b159!8m2!3d47.502481!4d-111.2903728!16s%2Fg%2F11fj3s7r_c!19sChIJ6fgNzB83QlMRWbFiI-u3Stk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:04:55.435Z</t>
+  </si>
+  <si>
+    <t>Jones Shannon DDS.</t>
+  </si>
+  <si>
+    <t>(406) 586-9725</t>
+  </si>
+  <si>
+    <t>3970 Valley Commons Dr Ste 1, Bozeman, MT 59718</t>
+  </si>
+  <si>
+    <t>Bozeman</t>
+  </si>
+  <si>
+    <t>SundayOpen 24 hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jones+Shannon+DDS./data=!4m7!3m6!1s0x5345444d5ee2395d:0x420affb306ae202!8m2!3d45.6721303!4d-111.0913492!16s%2Fg%2F1tj527x_!19sChIJXTniXk1ERVMRAuJqMPuvIAQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:06:27.616Z</t>
+  </si>
+  <si>
+    <t>Pearson Kevin DDS</t>
+  </si>
+  <si>
+    <t>(406) 587-7200</t>
+  </si>
+  <si>
+    <t>121 W Kagy Blvd, Bozeman, MT 59715</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pearson+Kevin+DDS/data=!4m7!3m6!1s0x5345451d0bf9d1b9:0xcc2b7df19b2d0055!8m2!3d45.6607463!4d-111.0397536!16s%2Fg%2F1w97v1c2!19sChIJudH5Cx1FRVMRVQAtm_F9K8w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:06:36.710Z</t>
+  </si>
+  <si>
+    <t>Hays Patrick R DDS</t>
+  </si>
+  <si>
+    <t>(406) 586-2117</t>
+  </si>
+  <si>
+    <t>1226 Stoneridge Dr, Bozeman, MT 59718</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hays+Patrick+R+DDS/data=!4m7!3m6!1s0x534545b30e2ce809:0xacf59290a6cbcce1!8m2!3d45.6916992!4d-111.0630294!16s%2Fg%2F1vhq3cjt!19sChIJCegsDrNFRVMR4czLppCS9aw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:06:57.962Z</t>
+  </si>
+  <si>
+    <t>robinson &amp; melzer family dental</t>
+  </si>
+  <si>
+    <t>(406) 587-7411</t>
+  </si>
+  <si>
+    <t>Doctor</t>
+  </si>
+  <si>
+    <t>4265 Fallon St, Bozeman, MT 59715</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/robinson+%26+melzer+family+dental/data=!4m7!3m6!1s0x5345458f01900001:0x2324e62677fa32ee!8m2!3d45.6740836!4d-111.096042!16s%2Fg%2F11d_bkwpzn!19sChIJAQCQAY9FRVMR7jL6dybmJCM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:07:26.482Z</t>
   </si>
 </sst>
 </file>
@@ -754,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1550,6 +1970,1031 @@
         <v>120</v>
       </c>
     </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" t="s">
+        <v>124</v>
+      </c>
+      <c r="M20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>130</v>
+      </c>
+      <c r="K21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" t="s">
+        <v>131</v>
+      </c>
+      <c r="M21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>130</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" t="s">
+        <v>136</v>
+      </c>
+      <c r="M22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" t="s">
+        <v>143</v>
+      </c>
+      <c r="J23" t="s">
+        <v>144</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>145</v>
+      </c>
+      <c r="M23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>147</v>
+      </c>
+      <c r="B24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E24" t="s">
+        <v>129</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>150</v>
+      </c>
+      <c r="I24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>151</v>
+      </c>
+      <c r="M24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>155</v>
+      </c>
+      <c r="E25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>130</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>156</v>
+      </c>
+      <c r="M25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E26" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>162</v>
+      </c>
+      <c r="M26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>166</v>
+      </c>
+      <c r="E27" t="s">
+        <v>167</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s">
+        <v>130</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>168</v>
+      </c>
+      <c r="M27" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" t="s">
+        <v>173</v>
+      </c>
+      <c r="E28" t="s">
+        <v>167</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" t="s">
+        <v>174</v>
+      </c>
+      <c r="M28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" t="s">
+        <v>179</v>
+      </c>
+      <c r="M29" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>181</v>
+      </c>
+      <c r="B30" t="s">
+        <v>182</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" t="s">
+        <v>167</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>184</v>
+      </c>
+      <c r="M30" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" t="s">
+        <v>187</v>
+      </c>
+      <c r="C31" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" t="s">
+        <v>188</v>
+      </c>
+      <c r="E31" t="s">
+        <v>167</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s">
+        <v>130</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>189</v>
+      </c>
+      <c r="M31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32" t="s">
+        <v>167</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>194</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>130</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" t="s">
+        <v>195</v>
+      </c>
+      <c r="M32" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>197</v>
+      </c>
+      <c r="B33" t="s">
+        <v>198</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>199</v>
+      </c>
+      <c r="E33" t="s">
+        <v>167</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>130</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>200</v>
+      </c>
+      <c r="M33" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>202</v>
+      </c>
+      <c r="B34" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>204</v>
+      </c>
+      <c r="E34" t="s">
+        <v>167</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>130</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>205</v>
+      </c>
+      <c r="M34" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>207</v>
+      </c>
+      <c r="B35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>209</v>
+      </c>
+      <c r="E35" t="s">
+        <v>167</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" t="s">
+        <v>83</v>
+      </c>
+      <c r="J35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>210</v>
+      </c>
+      <c r="M35" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>212</v>
+      </c>
+      <c r="B36" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>214</v>
+      </c>
+      <c r="E36" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" t="s">
+        <v>83</v>
+      </c>
+      <c r="J36" t="s">
+        <v>30</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>215</v>
+      </c>
+      <c r="M36" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>217</v>
+      </c>
+      <c r="B37" t="s">
+        <v>218</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>219</v>
+      </c>
+      <c r="E37" t="s">
+        <v>167</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" t="s">
+        <v>83</v>
+      </c>
+      <c r="J37" t="s">
+        <v>30</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>220</v>
+      </c>
+      <c r="M37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>222</v>
+      </c>
+      <c r="B38" t="s">
+        <v>223</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>224</v>
+      </c>
+      <c r="E38" t="s">
+        <v>167</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" t="s">
+        <v>83</v>
+      </c>
+      <c r="J38" t="s">
+        <v>130</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>225</v>
+      </c>
+      <c r="M38" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39" t="s">
+        <v>228</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>229</v>
+      </c>
+      <c r="E39" t="s">
+        <v>167</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>30</v>
+      </c>
+      <c r="I39" t="s">
+        <v>83</v>
+      </c>
+      <c r="J39" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>230</v>
+      </c>
+      <c r="M39" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>232</v>
+      </c>
+      <c r="B40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" t="s">
+        <v>234</v>
+      </c>
+      <c r="E40" t="s">
+        <v>167</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" t="s">
+        <v>83</v>
+      </c>
+      <c r="J40" t="s">
+        <v>30</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>235</v>
+      </c>
+      <c r="M40" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>237</v>
+      </c>
+      <c r="B41" t="s">
+        <v>238</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>239</v>
+      </c>
+      <c r="E41" t="s">
+        <v>240</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>241</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>242</v>
+      </c>
+      <c r="M41" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>244</v>
+      </c>
+      <c r="B42" t="s">
+        <v>245</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>246</v>
+      </c>
+      <c r="E42" t="s">
+        <v>240</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>247</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>30</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>248</v>
+      </c>
+      <c r="M42" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>250</v>
+      </c>
+      <c r="B43" t="s">
+        <v>251</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>252</v>
+      </c>
+      <c r="E43" t="s">
+        <v>240</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>30</v>
+      </c>
+      <c r="I43" t="s">
+        <v>83</v>
+      </c>
+      <c r="J43" t="s">
+        <v>130</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>253</v>
+      </c>
+      <c r="M43" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>255</v>
+      </c>
+      <c r="B44" t="s">
+        <v>256</v>
+      </c>
+      <c r="C44" t="s">
+        <v>257</v>
+      </c>
+      <c r="D44" t="s">
+        <v>258</v>
+      </c>
+      <c r="E44" t="s">
+        <v>240</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>30</v>
+      </c>
+      <c r="I44" t="s">
+        <v>83</v>
+      </c>
+      <c r="J44" t="s">
+        <v>130</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>259</v>
+      </c>
+      <c r="M44" t="s">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
